--- a/data/trans_orig/IP31KM03_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM03_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45805</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39966</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51066</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61489</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54809</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65367</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50502</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119507</t>
+          <t>91586</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109678</t>
+          <t>83231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126632</t>
+          <t>97890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14458</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9197</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20297</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6033</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16591</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80477</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71279</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>89352</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>103434</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>92825</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>116177</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89049</t>
+          <t>76785</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77368</t>
+          <t>68661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98513</t>
+          <t>83439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>192482</t>
+          <t>157262</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178528</t>
+          <t>145384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212577</t>
+          <t>168377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34474</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25599</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43672</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9472</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32824</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>30672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>45907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73543</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51058</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46259</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53988</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46067</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41298</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49758</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57665</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60773</t>
+          <t>48384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>95816</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97249</t>
+          <t>89325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109318</t>
+          <t>100810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9485</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5794</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14254</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57980</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50124</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63877</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50798</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43026</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56355</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>72,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>43858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69039</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>109890</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102948</t>
+          <t>98490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123194</t>
+          <t>118552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11836</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19692</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18884</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26656</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>30388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32803</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30131</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33888</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>73604</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70905</t>
+          <t>71059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74600</t>
+          <t>74692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>37426</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32553</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>41097</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>79,28%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>31051</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>26153</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>35171</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>59,05%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37483</t>
+          <t>25917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47027</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>67873</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67784</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9783</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14656</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13239</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18137</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30288</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>111065</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>101400</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>119827</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>79,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>72,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>85,24%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>104130</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>96107</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>110833</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>84,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>89,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>125184</t>
+          <t>103310</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>95644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133232</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>229314</t>
+          <t>214376</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216211</t>
+          <t>202199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>239971</t>
+          <t>225370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29506</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20744</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39171</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>19566</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12863</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>27589</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41305</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>49426</t>
+          <t>48018</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>60195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>150332</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>144029</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>154233</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>123733</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>126518</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>147805</t>
+          <t>132726</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141945</t>
+          <t>127680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151261</t>
+          <t>135588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>271536</t>
+          <t>283058</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>264693</t>
+          <t>275572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276435</t>
+          <t>288234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>4932</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9438</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>573722</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>554146</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>590560</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>553504</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>535855</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>570235</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>602396</t>
+          <t>504214</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>642254</t>
+          <t>534529</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1151284</t>
+          <t>1070568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1203148</t>
+          <t>1117360</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>113102</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>96264</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>132678</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>99630</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>82899</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>117279</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>83679</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142337</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>220309</t>
+          <t>211568</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>194719</t>
+          <t>187671</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246583</t>
+          <t>234463</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
